--- a/relatorio/Relatorio_de_Testes_CineLume.xlsx
+++ b/relatorio/Relatorio_de_Testes_CineLume.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aluno\Documents\GitHub\cinelume-qa\relatorio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36D11EFC-FB2F-4B48-A66E-499A8984A0E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BE178D8-F95E-4838-A6CA-C1F7F1910C8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="528">
   <si>
     <t>Relatório de Testes — CineLume v1.0</t>
   </si>
@@ -1544,46 +1544,100 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>o adicional do 3D</t>
-  </si>
-  <si>
-    <t>meia entrada</t>
-  </si>
-  <si>
-    <t>A uma brecha para escolhe quantidade de meia entrada antes dos assentos</t>
-  </si>
-  <si>
-    <t>o valor da sessão das 20:30</t>
-  </si>
-  <si>
-    <t>A error de valor</t>
-  </si>
-  <si>
-    <t>A contradição no valor da compra dos ingressos</t>
-  </si>
-  <si>
-    <t>O valor da pré-estreia</t>
-  </si>
-  <si>
-    <t>A uma brecha no calculo para aceita meia entrada</t>
-  </si>
-  <si>
-    <t>Error na escolha de quantidade de assentos</t>
-  </si>
-  <si>
-    <t>não tem quantidade certa para escolher assentos</t>
-  </si>
-  <si>
-    <t>Seleção de assentos</t>
-  </si>
-  <si>
-    <t>Ao troca de sala o sistema não reinicia os assentos</t>
-  </si>
-  <si>
-    <t>CUPOM CINE10</t>
-  </si>
-  <si>
-    <t>está com o valor a mais</t>
+    <t>A regra determina que a meia-entrada custa 50% do valor do ingresso (incluindo o adicional 3D). No entanto, sessões com valores bases ou adicionais que gerem números ímpares (ou quando combinadas com cupons percentuais)</t>
+  </si>
+  <si>
+    <t>O Conflito do Arredondamento da Meia-Entrada com Valores Ímpares</t>
+  </si>
+  <si>
+    <t>A RN09 diz que o cupom CINE10 dá 10% de desconto "apenas sobre o subtotal de ingressos". Contudo, o documento não especifica se esse desconto de 10% incide antes ou depois de somar a taxa de conveniência (RN08) ou se a base de cálculo exclui a taxa.</t>
+  </si>
+  <si>
+    <t>Falta de Tratamento para Limite Inferior de Meias-Entradas</t>
+  </si>
+  <si>
+    <t>A RN05 permite de 1 a 6 ingressos por pedido, e a RN03 diz que o número de meias não pode ser maior que o número de assentos. Porém, o documento omite se o número mínimo de meias pode ser 0 (permitindo apenas inteiras). Sem essa validação explícita no código, o sistema pode rejeitar pedidos 100% de inteiras exigindo obrigatoriamente pelo menos uma meia-entrada</t>
+  </si>
+  <si>
+    <t>Conflito Dinâmico no Desconto Pix com Cupons e Taxas</t>
+  </si>
+  <si>
+    <t>A RN11 define que o Pix dá 5% de desconto sobre o valor total do pedido (ingressos + taxa + bomboniere − cupom). Se o usuário alternar entre Pix e Cartão várias vezes (conforme o CA11.3 menciona), erros de arredondamento sucessivos em ponto flutuante (floating-point arithmetic) podem fazer o sistema acumular centavos de diferença ou estourar a trava de segurança de "nunca dar mais de 5%".</t>
+  </si>
+  <si>
+    <t>tratam da seleção de assentos e de marcá-los como ocupados após a confirmação. Porém, o escopo desconsidera integração com banco de dados real e não há especificação de concorrência (o que acontece se dois usuários clicarem no mesmo assento do mesmo navegador simulado ao mesmo tempo antes da confirmação, gerando "overbooking" virtual na sala).</t>
+  </si>
+  <si>
+    <t>Omissão da Regra para Estoque e Concorrência de Assentos (RN06 vs. RN15)</t>
+  </si>
+  <si>
+    <t>O critério CA13.3 valida o e-mail apenas exigindo a presença do caractere @ (nome@dominio.extensao). Essa validação é frágil e aceita strings inválidas como @dominio ou abc@.com, permitindo que cadastros falsos ou corrompidos avancem para a etapa de finalização.</t>
+  </si>
+  <si>
+    <t>Vazio Normativo sobre o Estorno do Pedido em Andamento</t>
+  </si>
+  <si>
+    <t>garante que apertar F5 preserva o pedido em andamento. Contudo, o documento não define um tempo de expiração (timeout) para esse carrinho temporário. Se o usuário selecionar assentos e fechar o navegador, esses assentos ficam presos no estado "em andamento" indefinidamente sem que outras pessoas consigam comprá-los.</t>
+  </si>
+  <si>
+    <t>Comportamento do Botão "Confirmar Compra" Múltiplo</t>
+  </si>
+  <si>
+    <t>exige que múltiplos cliques no botão de confirmação gerem apenas um registro. Porém, a RN14 diz que o botão exibe "Processando pagamento...". Se o sistema demorar alguns segundos na simulação e o usuário impaciente clicar 3 vezes seguidas rapidamente antes da tela de travamento entrar em vigor, o frontend pode disparar requisições duplicadas.</t>
+  </si>
+  <si>
+    <t>Falta de Restrição de Idade vs. Classificação Indicativa</t>
+  </si>
+  <si>
+    <t>: A tabela de filmes lista classificações indicativas rígidas (ex: Cidade de Vidro é para 16 anos), mas nenhuma regra de negócio (RN01 a RN21) exige que o sistema valide a idade do comprador ou exiba um pop-up de termo de responsabilidade antes de permitir a escolha de assentos para sessões restritas.</t>
+  </si>
+  <si>
+    <t>Incompatibilidade Lógica no Limite de Quantidade da Bomboniere</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> na Aplicação da Taxa de Conveniência com o Cupom CINE10</t>
+  </si>
+  <si>
+    <t>A RN07 estipula que cada produto da bomboniere aceita quantidades inteiras de 0 a 10 (com correção automática para 10 se passar). Porém, se um cliente adicionar 10 unidades de cada um dos 5 itens da bomboniere simultaneamente, o subtotal da bomboniere explodirá de forma irrealista sem nenhuma trava de quantidade total de itens por transação, podendo burlar a lógica do cupom PIPOCA5 de forma abusiva.</t>
+  </si>
+  <si>
+    <t>Permitir até 10 unidades de cada item simultaneamente sem um teto geral por transação pode gerar valores absurdos. Deve haver um limite máximo de itens por pedido ou uma trava de segurança para evitar abusos?</t>
+  </si>
+  <si>
+    <t>A tabela exibe classificações indicativas (ex: 16 anos), mas o fluxo de compra não valida a idade do usuário. O sistema deve bloquear a seleção de assentos ou exigir confirmação de idade para filmes restritos?</t>
+  </si>
+  <si>
+    <t>Para evitar que cliques múltiplos rápidos gerem registros duplicados antes da mensagem 'Processando pagamento...' aparecer, podemos desabilitar o botão de confirmação (pointer-events: none / disabled) imediatamente no primeiro clique?</t>
+  </si>
+  <si>
+    <t>O pedido é mantido ao recarregar a página (F5), mas há um tempo limite de expiração para esse carrinho? Se o usuário fechar a aba, por quanto tempo os assentos selecionados ficam travados bloqueando outros compradores?</t>
+  </si>
+  <si>
+    <t>A regra atual exige apenas a presença de '@' no e-mail. Podemos substituir a validação por uma Expressão Regular (Regex) robusta para impedir a entrada de e-mails mal formatados ou incompletos?</t>
+  </si>
+  <si>
+    <t>O que acontece no sistema se dois usuários tentarem selecionar e comprar o mesmo assento simultaneamente antes da confirmação? Precisamos de um mecanismo de lock temporário ou validação de assentos ocupados no momento do checkout.</t>
+  </si>
+  <si>
+    <t>Ao alternar repetidamente entre meios de pagamento (Cartão/Pix), a aplicação do desconto dinâmico de 5% pode gerar resíduos em ponto flutuante (ex: R$ 0,001 de diferença). Podemos padronizar o arredondamento para 2 casas decimais logo após calcular a porcentagem do Pix?</t>
+  </si>
+  <si>
+    <t>A RN05 permite de 1 a 6 ingressos, mas a RN03 não especifica se a quantidade de meias pode ser zero (100% de inteiras). O sistema deve permitir pedidos sem nenhuma meia-entrada sem disparar erros de validação?</t>
+  </si>
+  <si>
+    <t>O desconto de 10% do cupom CINE10 deve incidir estritamente sobre o valor bruto dos ingressos antes de somar a taxa de conveniência (R$ 2,50 por ingresso), ou a taxa também entra na base de cálculo? Favor esclarecer a ordem exata das operações no código.</t>
+  </si>
+  <si>
+    <t>Como o sistema deve tratar os centavos resultantes do cálculo de 50% em valores ímpares (ex: truncar, arredondar para cima ou para baixo)? Precisamos definir uma função padrão de arredondamento monetário para evitar divergências no caixa.</t>
+  </si>
+  <si>
+    <t>validar com teste funcionais detalhadamente a conformidade e regras de negocios do sistema</t>
+  </si>
+  <si>
+    <t>validação de E-mail Excessivamente Simples</t>
+  </si>
+  <si>
+    <t>validar quantidade de meia entrada por assentos,executar aplicação do cupom,testa o fluxo do botao de corfimação da compra, testa de restrição de idade</t>
   </si>
 </sst>
 </file>
@@ -1731,9 +1785,6 @@
   </cellStyleXfs>
   <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1773,6 +1824,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2047,206 +2101,206 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="5"/>
+      <c r="B4" s="4"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="7"/>
-      <c r="B13" s="5"/>
+      <c r="A13" s="6"/>
+      <c r="B13" s="4"/>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="5"/>
+      <c r="B14" s="4"/>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="4" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="4" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="4" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="4" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="4" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="4" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="4" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="4" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="4" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="7"/>
-      <c r="B24" s="5"/>
+      <c r="A24" s="6"/>
+      <c r="B24" s="4"/>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B25" s="5"/>
+      <c r="B25" s="4"/>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="4" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" s="6" t="s">
+      <c r="A28" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="4" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="4" t="s">
         <v>46</v>
       </c>
     </row>
@@ -2272,330 +2326,330 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>324</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>325</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="10" t="s">
         <v>326</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="10" t="s">
         <v>327</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="10" t="s">
         <v>328</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="10" t="s">
         <v>329</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="10" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="14" t="s">
         <v>330</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="14" t="s">
         <v>331</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="14" t="s">
         <v>332</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="14" t="s">
         <v>333</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="14" t="s">
         <v>334</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="14" t="s">
         <v>334</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="I5" s="15"/>
+      <c r="I5" s="14"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>335</v>
       </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>336</v>
       </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>337</v>
       </c>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>338</v>
       </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>339</v>
       </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>340</v>
       </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="7" t="s">
         <v>341</v>
       </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="7" t="s">
         <v>342</v>
       </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="7" t="s">
         <v>343</v>
       </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="7" t="s">
         <v>344</v>
       </c>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="7" t="s">
         <v>345</v>
       </c>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="7" t="s">
         <v>346</v>
       </c>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="7" t="s">
         <v>347</v>
       </c>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="7" t="s">
         <v>348</v>
       </c>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="7" t="s">
         <v>349</v>
       </c>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="7" t="s">
         <v>350</v>
       </c>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="7" t="s">
         <v>351</v>
       </c>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="7" t="s">
         <v>352</v>
       </c>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="7" t="s">
         <v>353</v>
       </c>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="7" t="s">
         <v>354</v>
       </c>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2654,100 +2708,100 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>357</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>358</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="10" t="s">
         <v>359</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="10" t="s">
         <v>360</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="10" t="s">
         <v>361</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="10" t="s">
         <v>362</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="10" t="s">
         <v>363</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="J4" s="10" t="s">
         <v>364</v>
       </c>
-      <c r="K4" s="11" t="s">
+      <c r="K4" s="10" t="s">
         <v>365</v>
       </c>
-      <c r="L4" s="11" t="s">
+      <c r="L4" s="10" t="s">
         <v>366</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>367</v>
       </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
     </row>
     <row r="6" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>368</v>
       </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
-      <c r="L6" s="9"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
     </row>
     <row r="7" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>369</v>
       </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2790,263 +2844,263 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="15" t="s">
         <v>372</v>
       </c>
-      <c r="B4" s="17"/>
+      <c r="B4" s="16"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="17" t="s">
         <v>373</v>
       </c>
-      <c r="B5" s="19">
+      <c r="B5" s="18">
         <f>COUNTA('5_Casos_de_Teste'!G6:G45)</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="17" t="s">
         <v>374</v>
       </c>
-      <c r="B6" s="19">
+      <c r="B6" s="18">
         <f>COUNTIF('5_Casos_de_Teste'!M6:M45,"Passou")</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="17" t="s">
         <v>375</v>
       </c>
-      <c r="B7" s="19">
+      <c r="B7" s="18">
         <f>COUNTIF('5_Casos_de_Teste'!M6:M45,"Falhou")</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="17" t="s">
         <v>376</v>
       </c>
-      <c r="B8" s="19">
+      <c r="B8" s="18">
         <f>COUNTIF('5_Casos_de_Teste'!M6:M45,"Bloqueado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="17" t="s">
         <v>377</v>
       </c>
-      <c r="B9" s="19">
+      <c r="B9" s="18">
         <f>COUNTIF('5_Casos_de_Teste'!M6:M45,"Não executado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="17" t="s">
         <v>378</v>
       </c>
-      <c r="B10" s="20">
+      <c r="B10" s="19">
         <f>IFERROR(B6/(B6+B7+B8),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="17" t="s">
         <v>379</v>
       </c>
-      <c r="B11" s="19">
+      <c r="B11" s="18">
         <f>COUNTIF('5_Casos_de_Teste'!D6:D45,"Valor limite")</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="18" t="s">
+      <c r="A12" s="17" t="s">
         <v>380</v>
       </c>
-      <c r="B12" s="19">
+      <c r="B12" s="18">
         <f>COUNTA('6_Bugs'!B6:B35)</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="17" t="s">
         <v>381</v>
       </c>
-      <c r="B13" s="19">
+      <c r="B13" s="18">
         <f>COUNTIF('6_Bugs'!G6:G35,"Crítica")</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="17" t="s">
         <v>382</v>
       </c>
-      <c r="B14" s="19">
+      <c r="B14" s="18">
         <f>COUNTIF('6_Bugs'!G6:G35,"Alta")</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="17" t="s">
         <v>383</v>
       </c>
-      <c r="B15" s="19">
+      <c r="B15" s="18">
         <f>COUNTIF('6_Bugs'!G6:G35,"Média")</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="18" t="s">
+      <c r="A16" s="17" t="s">
         <v>384</v>
       </c>
-      <c r="B16" s="19">
+      <c r="B16" s="18">
         <f>COUNTIF('6_Bugs'!G6:G35,"Baixa")</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="18" t="s">
+      <c r="A17" s="17" t="s">
         <v>385</v>
       </c>
-      <c r="B17" s="19">
+      <c r="B17" s="18">
         <f>COUNTIF('6_Bugs'!N6:N35,"Corrigido*")</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="18" t="s">
+      <c r="A18" s="17" t="s">
         <v>386</v>
       </c>
-      <c r="B18" s="19">
+      <c r="B18" s="18">
         <f>COUNTA('7_Nao_Funcionais'!H6:H20)</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="18" t="s">
+      <c r="A19" s="17" t="s">
         <v>387</v>
       </c>
-      <c r="B19" s="19">
+      <c r="B19" s="18">
         <f>COUNTIF('7_Nao_Funcionais'!H6:H20,"Falhou")</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="18" t="s">
+      <c r="A20" s="17" t="s">
         <v>388</v>
       </c>
-      <c r="B20" s="19">
+      <c r="B20" s="18">
         <f>COUNTA('8_Caixa_Branca'!C6:C25)</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="18" t="s">
+      <c r="A21" s="17" t="s">
         <v>389</v>
       </c>
-      <c r="B21" s="19">
+      <c r="B21" s="18">
         <f>COUNTA('9_Automacao'!E6:E25)</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="18" t="s">
+      <c r="A22" s="17" t="s">
         <v>390</v>
       </c>
-      <c r="B22" s="19">
+      <c r="B22" s="18">
         <f>COUNTIF('9_Automacao'!H6:H25,"Passou")</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="18" t="s">
+      <c r="A23" s="17" t="s">
         <v>391</v>
       </c>
-      <c r="B23" s="19">
+      <c r="B23" s="18">
         <f>COUNTIF('9_Automacao'!H6:H25,"Falhou")</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="16" t="s">
+      <c r="A25" s="15" t="s">
         <v>392</v>
       </c>
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="16"/>
     </row>
     <row r="26" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="7" t="s">
         <v>393</v>
       </c>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="10" t="s">
+      <c r="B26" s="22"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="9" t="s">
         <v>394</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="7" t="s">
         <v>395</v>
       </c>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
+      <c r="B27" s="22"/>
+      <c r="C27" s="22"/>
     </row>
     <row r="28" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="7" t="s">
         <v>396</v>
       </c>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
+      <c r="B28" s="22"/>
+      <c r="C28" s="22"/>
     </row>
     <row r="29" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="7" t="s">
         <v>397</v>
       </c>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
+      <c r="B29" s="22"/>
+      <c r="C29" s="22"/>
     </row>
     <row r="30" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="8" t="s">
+      <c r="A30" s="7" t="s">
         <v>398</v>
       </c>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="10" t="s">
+      <c r="B30" s="22"/>
+      <c r="C30" s="22"/>
+      <c r="D30" s="9" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="7" t="s">
         <v>400</v>
       </c>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="10" t="s">
+      <c r="B31" s="22"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="9" t="s">
         <v>401</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="7" t="s">
         <v>402</v>
       </c>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
+      <c r="B32" s="22"/>
+      <c r="C32" s="22"/>
     </row>
     <row r="33" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="7" t="s">
         <v>403</v>
       </c>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
+      <c r="B33" s="22"/>
+      <c r="C33" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -3094,147 +3148,147 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>406</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="10" t="s">
         <v>407</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="10" t="s">
         <v>408</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="10" t="s">
         <v>409</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="10" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>411</v>
       </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>412</v>
       </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>413</v>
       </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>414</v>
       </c>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>415</v>
       </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>416</v>
       </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>417</v>
       </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="7" t="s">
         <v>418</v>
       </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="7" t="s">
         <v>419</v>
       </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="7" t="s">
         <v>420</v>
       </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3263,382 +3317,382 @@
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>421</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>422</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>423</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="5" t="s">
         <v>424</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="5" t="s">
         <v>425</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="5" t="s">
         <v>426</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" s="5" t="s">
         <v>427</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="M1" s="5" t="s">
         <v>428</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="N1" s="5" t="s">
         <v>429</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="O1" s="5" t="s">
         <v>430</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="P1" s="5" t="s">
         <v>431</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>432</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>433</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="6" t="s">
         <v>434</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="6" t="s">
         <v>435</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="K2" s="6" t="s">
         <v>436</v>
       </c>
-      <c r="L2" s="7" t="s">
+      <c r="L2" s="6" t="s">
         <v>437</v>
       </c>
-      <c r="M2" s="7" t="s">
+      <c r="M2" s="6" t="s">
         <v>438</v>
       </c>
-      <c r="N2" s="7" t="s">
+      <c r="N2" s="6" t="s">
         <v>439</v>
       </c>
-      <c r="O2" s="7" t="s">
+      <c r="O2" s="6" t="s">
         <v>440</v>
       </c>
-      <c r="P2" s="7" t="s">
+      <c r="P2" s="6" t="s">
         <v>441</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="6" t="s">
         <v>442</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>443</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="6" t="s">
         <v>444</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="6" t="s">
         <v>445</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="6" t="s">
         <v>446</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="6" t="s">
         <v>447</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="6" t="s">
         <v>445</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="K3" s="6" t="s">
         <v>448</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="6" t="s">
         <v>449</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="M3" s="6" t="s">
         <v>450</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="N3" s="6" t="s">
         <v>451</v>
       </c>
-      <c r="O3" s="7" t="s">
+      <c r="O3" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="P3" s="7" t="s">
+      <c r="P3" s="6" t="s">
         <v>452</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="6" t="s">
         <v>453</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>454</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="6" t="s">
         <v>455</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="6" t="s">
         <v>456</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="L4" s="6" t="s">
         <v>457</v>
       </c>
-      <c r="M4" s="7" t="s">
+      <c r="M4" s="6" t="s">
         <v>458</v>
       </c>
-      <c r="N4" s="7" t="s">
+      <c r="N4" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="O4" s="7" t="s">
+      <c r="O4" s="6" t="s">
         <v>459</v>
       </c>
-      <c r="P4" s="7" t="s">
+      <c r="P4" s="6" t="s">
         <v>460</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="6" t="s">
         <v>461</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>462</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="6" t="s">
         <v>463</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="6" t="s">
         <v>464</v>
       </c>
-      <c r="M5" s="7" t="s">
+      <c r="M5" s="6" t="s">
         <v>465</v>
       </c>
-      <c r="N5" s="7" t="s">
+      <c r="N5" s="6" t="s">
         <v>466</v>
       </c>
-      <c r="O5" s="7" t="s">
+      <c r="O5" s="6" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="6" t="s">
         <v>468</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>426</v>
       </c>
-      <c r="M6" s="7" t="s">
+      <c r="M6" s="6" t="s">
         <v>469</v>
       </c>
-      <c r="N6" s="7" t="s">
+      <c r="N6" s="6" t="s">
         <v>470</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="6" t="s">
         <v>471</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>472</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="M7" s="7" t="s">
+      <c r="M7" s="6" t="s">
         <v>473</v>
       </c>
-      <c r="N7" s="7" t="s">
+      <c r="N7" s="6" t="s">
         <v>474</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="6" t="s">
         <v>475</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>476</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="M8" s="7" t="s">
+      <c r="M8" s="6" t="s">
         <v>477</v>
       </c>
-      <c r="N8" s="7" t="s">
+      <c r="N8" s="6" t="s">
         <v>478</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="6" t="s">
         <v>480</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="M9" s="7" t="s">
+      <c r="M9" s="6" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="6" t="s">
         <v>481</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="M10" s="7" t="s">
+      <c r="M10" s="6" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="M11" s="7" t="s">
+      <c r="M11" s="6" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="6" t="s">
         <v>483</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="M12" s="7" t="s">
+      <c r="M12" s="6" t="s">
         <v>484</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="6" t="s">
         <v>485</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="6" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="6" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="6" t="s">
         <v>486</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="6" t="s">
         <v>487</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="6" t="s">
         <v>488</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="6" t="s">
         <v>489</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="6" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="6" t="s">
         <v>490</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="6" t="s">
         <v>491</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="6" t="s">
         <v>492</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="6" t="s">
         <v>493</v>
       </c>
     </row>
@@ -3658,78 +3712,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="9"/>
+      <c r="B4" s="8"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="B5" s="9"/>
+      <c r="B5" s="8"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="10" t="s">
+      <c r="B6" s="8"/>
+      <c r="C6" s="9" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="10" t="s">
+      <c r="B7" s="8"/>
+      <c r="C7" s="9" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="B8" s="9"/>
-      <c r="C8" s="10" t="s">
+      <c r="B8" s="8"/>
+      <c r="C8" s="9" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="10" t="s">
+      <c r="B9" s="8"/>
+      <c r="C9" s="9" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="10" t="s">
+      <c r="B10" s="8"/>
+      <c r="C10" s="9" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="10" t="s">
+      <c r="B11" s="8"/>
+      <c r="C11" s="9" t="s">
         <v>60</v>
       </c>
     </row>
@@ -3751,138 +3805,138 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="10" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="8" t="s">
         <v>494</v>
       </c>
-      <c r="D5" s="9"/>
+      <c r="D5" s="8"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="8" t="s">
         <v>494</v>
       </c>
-      <c r="D6" s="9"/>
+      <c r="D6" s="8"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="8" t="s">
         <v>494</v>
       </c>
-      <c r="D7" s="9"/>
+      <c r="D7" s="8"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="8" t="s">
         <v>494</v>
       </c>
-      <c r="D8" s="9"/>
+      <c r="D8" s="8"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="8" t="s">
         <v>494</v>
       </c>
-      <c r="D9" s="9"/>
+      <c r="D9" s="8"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="8" t="s">
         <v>494</v>
       </c>
-      <c r="D10" s="9"/>
+      <c r="D10" s="8"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="8" t="s">
         <v>494</v>
       </c>
-      <c r="D11" s="9"/>
+      <c r="D11" s="8"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="8" t="s">
         <v>494</v>
       </c>
-      <c r="D12" s="9"/>
+      <c r="D12" s="8"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="13" t="s">
+      <c r="A15" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="13" t="s">
         <v>436</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="13" t="s">
+      <c r="A16" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="B16" s="14"/>
+      <c r="B16" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3927,210 +3981,254 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="10" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="14" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+    <row r="6" spans="1:6" ht="66" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="8" t="s">
         <v>453</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="8" t="s">
         <v>497</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="8" t="s">
+        <v>496</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="66" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>440</v>
+      </c>
+      <c r="E7" s="8" t="s">
         <v>498</v>
       </c>
-      <c r="F6" s="9"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>442</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>496</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>459</v>
-      </c>
-      <c r="E7" s="9" t="s">
+      <c r="F7" s="8" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="92.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>468</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>499</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>500</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="92.4" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>483</v>
+      </c>
+      <c r="C9" s="21" t="s">
         <v>501</v>
       </c>
-      <c r="F7" s="9"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>453</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>499</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>459</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>500</v>
-      </c>
-      <c r="F8" s="9"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>461</v>
-      </c>
-      <c r="C9" s="22" t="s">
+      <c r="D9" s="8" t="s">
+        <v>467</v>
+      </c>
+      <c r="E9" s="21" t="s">
         <v>502</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="F9" s="8" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="92.4" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>488</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>504</v>
+      </c>
+      <c r="D10" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="E9" s="22" t="s">
+      <c r="E10" s="21" t="s">
         <v>503</v>
       </c>
-      <c r="F9" s="9"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>468</v>
-      </c>
-      <c r="C10" s="22" t="s">
-        <v>504</v>
-      </c>
-      <c r="D10" s="9" t="s">
+      <c r="F10" s="8" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="66" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>526</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>467</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>505</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="79.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>489</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>506</v>
+      </c>
+      <c r="D12" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="E10" s="22" t="s">
-        <v>505</v>
-      </c>
-      <c r="F10" s="9"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>471</v>
-      </c>
-      <c r="C11" s="22" t="s">
-        <v>506</v>
-      </c>
-      <c r="D11" s="9" t="s">
+      <c r="E12" s="21" t="s">
+        <v>507</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="92.4" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>488</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>508</v>
+      </c>
+      <c r="D13" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="E11" s="22" t="s">
-        <v>507</v>
-      </c>
-      <c r="F11" s="9"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>481</v>
-      </c>
-      <c r="C12" s="21" t="s">
-        <v>508</v>
-      </c>
-      <c r="D12" s="9" t="s">
+      <c r="E13" s="8" t="s">
+        <v>509</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="79.2" x14ac:dyDescent="0.3">
+      <c r="A14" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>432</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>510</v>
+      </c>
+      <c r="D14" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="E12" s="22" t="s">
-        <v>509</v>
-      </c>
-      <c r="F12" s="9"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="8" t="s">
+      <c r="E14" s="8" t="s">
+        <v>511</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="105.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
+      <c r="B15" s="8" t="s">
+        <v>475</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>512</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>440</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>515</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4173,204 +4271,208 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>495</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="B4" s="9"/>
+      <c r="B4" s="8" t="s">
+        <v>525</v>
+      </c>
     </row>
     <row r="5" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="10" t="s">
+      <c r="B5" s="8" t="s">
+        <v>527</v>
+      </c>
+      <c r="C5" s="9" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="B6" s="9"/>
+      <c r="B6" s="8"/>
     </row>
     <row r="7" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="10" t="s">
+      <c r="B7" s="8"/>
+      <c r="C7" s="9" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="B8" s="9"/>
+      <c r="B8" s="8"/>
     </row>
     <row r="9" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="10" t="s">
+      <c r="B9" s="8"/>
+      <c r="C9" s="9" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="10" t="s">
+      <c r="B10" s="8"/>
+      <c r="C10" s="9" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="10" t="s">
+      <c r="B11" s="8"/>
+      <c r="C11" s="9" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="10" t="s">
+      <c r="B12" s="8"/>
+      <c r="C12" s="9" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="10" t="s">
+      <c r="B13" s="8"/>
+      <c r="C13" s="9" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="10" t="s">
+      <c r="B14" s="8"/>
+      <c r="C14" s="9" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="3" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="10" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="13" t="s">
+      <c r="A19" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="13" t="s">
+      <c r="A20" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="13" t="s">
+      <c r="A21" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="13" t="s">
+      <c r="A22" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="13" t="s">
+      <c r="A23" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="13" t="s">
+      <c r="A24" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="13" t="s">
+      <c r="A25" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="13" t="s">
+      <c r="A26" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="13" t="s">
+      <c r="A27" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="13" t="s">
+      <c r="A28" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="13" t="s">
+      <c r="A29" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="13" t="s">
+      <c r="A30" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4424,864 +4526,864 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="J4" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="K4" s="11" t="s">
+      <c r="K4" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="L4" s="11" t="s">
+      <c r="L4" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="M4" s="11" t="s">
+      <c r="M4" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="N4" s="11" t="s">
+      <c r="N4" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="O4" s="11" t="s">
+      <c r="O4" s="10" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="14" t="s">
         <v>160</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="14" t="s">
         <v>164</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="I5" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="J5" s="15" t="s">
+      <c r="J5" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="K5" s="15" t="s">
+      <c r="K5" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="L5" s="15" t="s">
+      <c r="L5" s="14" t="s">
         <v>168</v>
       </c>
-      <c r="M5" s="15" t="s">
+      <c r="M5" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="N5" s="15"/>
-      <c r="O5" s="15"/>
+      <c r="N5" s="14"/>
+      <c r="O5" s="14"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
-      <c r="L6" s="9"/>
-      <c r="M6" s="9"/>
-      <c r="N6" s="9"/>
-      <c r="O6" s="9"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="8"/>
+      <c r="N6" s="8"/>
+      <c r="O6" s="8"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9"/>
-      <c r="N7" s="9"/>
-      <c r="O7" s="9"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="9"/>
-      <c r="M8" s="9"/>
-      <c r="N8" s="9"/>
-      <c r="O8" s="9"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
-      <c r="N9" s="9"/>
-      <c r="O9" s="9"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="8"/>
+      <c r="O9" s="8"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="9"/>
-      <c r="L10" s="9"/>
-      <c r="M10" s="9"/>
-      <c r="N10" s="9"/>
-      <c r="O10" s="9"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
-      <c r="L11" s="9"/>
-      <c r="M11" s="9"/>
-      <c r="N11" s="9"/>
-      <c r="O11" s="9"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="8"/>
+      <c r="O11" s="8"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="9"/>
-      <c r="M12" s="9"/>
-      <c r="N12" s="9"/>
-      <c r="O12" s="9"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="9"/>
-      <c r="M13" s="9"/>
-      <c r="N13" s="9"/>
-      <c r="O13" s="9"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="8"/>
+      <c r="N13" s="8"/>
+      <c r="O13" s="8"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="9"/>
-      <c r="N14" s="9"/>
-      <c r="O14" s="9"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="8"/>
+      <c r="O14" s="8"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
-      <c r="K15" s="9"/>
-      <c r="L15" s="9"/>
-      <c r="M15" s="9"/>
-      <c r="N15" s="9"/>
-      <c r="O15" s="9"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="8"/>
+      <c r="N15" s="8"/>
+      <c r="O15" s="8"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
-      <c r="K16" s="9"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="9"/>
-      <c r="O16" s="9"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="8"/>
+      <c r="O16" s="8"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
-      <c r="K17" s="9"/>
-      <c r="L17" s="9"/>
-      <c r="M17" s="9"/>
-      <c r="N17" s="9"/>
-      <c r="O17" s="9"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="8"/>
+      <c r="N17" s="8"/>
+      <c r="O17" s="8"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
-      <c r="M18" s="9"/>
-      <c r="N18" s="9"/>
-      <c r="O18" s="9"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="8"/>
+      <c r="N18" s="8"/>
+      <c r="O18" s="8"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
-      <c r="K19" s="9"/>
-      <c r="L19" s="9"/>
-      <c r="M19" s="9"/>
-      <c r="N19" s="9"/>
-      <c r="O19" s="9"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="8"/>
+      <c r="M19" s="8"/>
+      <c r="N19" s="8"/>
+      <c r="O19" s="8"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
-      <c r="K20" s="9"/>
-      <c r="L20" s="9"/>
-      <c r="M20" s="9"/>
-      <c r="N20" s="9"/>
-      <c r="O20" s="9"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="8"/>
+      <c r="N20" s="8"/>
+      <c r="O20" s="8"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="9"/>
-      <c r="K21" s="9"/>
-      <c r="L21" s="9"/>
-      <c r="M21" s="9"/>
-      <c r="N21" s="9"/>
-      <c r="O21" s="9"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="8"/>
+      <c r="N21" s="8"/>
+      <c r="O21" s="8"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="9"/>
-      <c r="K22" s="9"/>
-      <c r="L22" s="9"/>
-      <c r="M22" s="9"/>
-      <c r="N22" s="9"/>
-      <c r="O22" s="9"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="8"/>
+      <c r="N22" s="8"/>
+      <c r="O22" s="8"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="9"/>
-      <c r="K23" s="9"/>
-      <c r="L23" s="9"/>
-      <c r="M23" s="9"/>
-      <c r="N23" s="9"/>
-      <c r="O23" s="9"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="8"/>
+      <c r="N23" s="8"/>
+      <c r="O23" s="8"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="9"/>
-      <c r="K24" s="9"/>
-      <c r="L24" s="9"/>
-      <c r="M24" s="9"/>
-      <c r="N24" s="9"/>
-      <c r="O24" s="9"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+      <c r="N24" s="8"/>
+      <c r="O24" s="8"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="9"/>
-      <c r="K25" s="9"/>
-      <c r="L25" s="9"/>
-      <c r="M25" s="9"/>
-      <c r="N25" s="9"/>
-      <c r="O25" s="9"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="8"/>
+      <c r="K25" s="8"/>
+      <c r="L25" s="8"/>
+      <c r="M25" s="8"/>
+      <c r="N25" s="8"/>
+      <c r="O25" s="8"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="9"/>
-      <c r="J26" s="9"/>
-      <c r="K26" s="9"/>
-      <c r="L26" s="9"/>
-      <c r="M26" s="9"/>
-      <c r="N26" s="9"/>
-      <c r="O26" s="9"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="8"/>
+      <c r="K26" s="8"/>
+      <c r="L26" s="8"/>
+      <c r="M26" s="8"/>
+      <c r="N26" s="8"/>
+      <c r="O26" s="8"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="9"/>
-      <c r="J27" s="9"/>
-      <c r="K27" s="9"/>
-      <c r="L27" s="9"/>
-      <c r="M27" s="9"/>
-      <c r="N27" s="9"/>
-      <c r="O27" s="9"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
+      <c r="J27" s="8"/>
+      <c r="K27" s="8"/>
+      <c r="L27" s="8"/>
+      <c r="M27" s="8"/>
+      <c r="N27" s="8"/>
+      <c r="O27" s="8"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
-      <c r="J28" s="9"/>
-      <c r="K28" s="9"/>
-      <c r="L28" s="9"/>
-      <c r="M28" s="9"/>
-      <c r="N28" s="9"/>
-      <c r="O28" s="9"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8"/>
+      <c r="J28" s="8"/>
+      <c r="K28" s="8"/>
+      <c r="L28" s="8"/>
+      <c r="M28" s="8"/>
+      <c r="N28" s="8"/>
+      <c r="O28" s="8"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="9"/>
-      <c r="J29" s="9"/>
-      <c r="K29" s="9"/>
-      <c r="L29" s="9"/>
-      <c r="M29" s="9"/>
-      <c r="N29" s="9"/>
-      <c r="O29" s="9"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="8"/>
+      <c r="J29" s="8"/>
+      <c r="K29" s="8"/>
+      <c r="L29" s="8"/>
+      <c r="M29" s="8"/>
+      <c r="N29" s="8"/>
+      <c r="O29" s="8"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A30" s="8" t="s">
+      <c r="A30" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="9"/>
-      <c r="J30" s="9"/>
-      <c r="K30" s="9"/>
-      <c r="L30" s="9"/>
-      <c r="M30" s="9"/>
-      <c r="N30" s="9"/>
-      <c r="O30" s="9"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="8"/>
+      <c r="J30" s="8"/>
+      <c r="K30" s="8"/>
+      <c r="L30" s="8"/>
+      <c r="M30" s="8"/>
+      <c r="N30" s="8"/>
+      <c r="O30" s="8"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="9"/>
-      <c r="J31" s="9"/>
-      <c r="K31" s="9"/>
-      <c r="L31" s="9"/>
-      <c r="M31" s="9"/>
-      <c r="N31" s="9"/>
-      <c r="O31" s="9"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="8"/>
+      <c r="I31" s="8"/>
+      <c r="J31" s="8"/>
+      <c r="K31" s="8"/>
+      <c r="L31" s="8"/>
+      <c r="M31" s="8"/>
+      <c r="N31" s="8"/>
+      <c r="O31" s="8"/>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="9"/>
-      <c r="J32" s="9"/>
-      <c r="K32" s="9"/>
-      <c r="L32" s="9"/>
-      <c r="M32" s="9"/>
-      <c r="N32" s="9"/>
-      <c r="O32" s="9"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="8"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="8"/>
+      <c r="I32" s="8"/>
+      <c r="J32" s="8"/>
+      <c r="K32" s="8"/>
+      <c r="L32" s="8"/>
+      <c r="M32" s="8"/>
+      <c r="N32" s="8"/>
+      <c r="O32" s="8"/>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="9"/>
-      <c r="J33" s="9"/>
-      <c r="K33" s="9"/>
-      <c r="L33" s="9"/>
-      <c r="M33" s="9"/>
-      <c r="N33" s="9"/>
-      <c r="O33" s="9"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="8"/>
+      <c r="I33" s="8"/>
+      <c r="J33" s="8"/>
+      <c r="K33" s="8"/>
+      <c r="L33" s="8"/>
+      <c r="M33" s="8"/>
+      <c r="N33" s="8"/>
+      <c r="O33" s="8"/>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A34" s="8" t="s">
+      <c r="A34" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="9"/>
-      <c r="J34" s="9"/>
-      <c r="K34" s="9"/>
-      <c r="L34" s="9"/>
-      <c r="M34" s="9"/>
-      <c r="N34" s="9"/>
-      <c r="O34" s="9"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="8"/>
+      <c r="I34" s="8"/>
+      <c r="J34" s="8"/>
+      <c r="K34" s="8"/>
+      <c r="L34" s="8"/>
+      <c r="M34" s="8"/>
+      <c r="N34" s="8"/>
+      <c r="O34" s="8"/>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A35" s="8" t="s">
+      <c r="A35" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="9"/>
-      <c r="I35" s="9"/>
-      <c r="J35" s="9"/>
-      <c r="K35" s="9"/>
-      <c r="L35" s="9"/>
-      <c r="M35" s="9"/>
-      <c r="N35" s="9"/>
-      <c r="O35" s="9"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="8"/>
+      <c r="I35" s="8"/>
+      <c r="J35" s="8"/>
+      <c r="K35" s="8"/>
+      <c r="L35" s="8"/>
+      <c r="M35" s="8"/>
+      <c r="N35" s="8"/>
+      <c r="O35" s="8"/>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A36" s="8" t="s">
+      <c r="A36" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="B36" s="9"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
-      <c r="H36" s="9"/>
-      <c r="I36" s="9"/>
-      <c r="J36" s="9"/>
-      <c r="K36" s="9"/>
-      <c r="L36" s="9"/>
-      <c r="M36" s="9"/>
-      <c r="N36" s="9"/>
-      <c r="O36" s="9"/>
+      <c r="B36" s="8"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="8"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="8"/>
+      <c r="I36" s="8"/>
+      <c r="J36" s="8"/>
+      <c r="K36" s="8"/>
+      <c r="L36" s="8"/>
+      <c r="M36" s="8"/>
+      <c r="N36" s="8"/>
+      <c r="O36" s="8"/>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A37" s="8" t="s">
+      <c r="A37" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="B37" s="9"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="9"/>
-      <c r="I37" s="9"/>
-      <c r="J37" s="9"/>
-      <c r="K37" s="9"/>
-      <c r="L37" s="9"/>
-      <c r="M37" s="9"/>
-      <c r="N37" s="9"/>
-      <c r="O37" s="9"/>
+      <c r="B37" s="8"/>
+      <c r="C37" s="8"/>
+      <c r="D37" s="8"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="8"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="8"/>
+      <c r="I37" s="8"/>
+      <c r="J37" s="8"/>
+      <c r="K37" s="8"/>
+      <c r="L37" s="8"/>
+      <c r="M37" s="8"/>
+      <c r="N37" s="8"/>
+      <c r="O37" s="8"/>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A38" s="8" t="s">
+      <c r="A38" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="B38" s="9"/>
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="9"/>
-      <c r="H38" s="9"/>
-      <c r="I38" s="9"/>
-      <c r="J38" s="9"/>
-      <c r="K38" s="9"/>
-      <c r="L38" s="9"/>
-      <c r="M38" s="9"/>
-      <c r="N38" s="9"/>
-      <c r="O38" s="9"/>
+      <c r="B38" s="8"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="8"/>
+      <c r="E38" s="8"/>
+      <c r="F38" s="8"/>
+      <c r="G38" s="8"/>
+      <c r="H38" s="8"/>
+      <c r="I38" s="8"/>
+      <c r="J38" s="8"/>
+      <c r="K38" s="8"/>
+      <c r="L38" s="8"/>
+      <c r="M38" s="8"/>
+      <c r="N38" s="8"/>
+      <c r="O38" s="8"/>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A39" s="8" t="s">
+      <c r="A39" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="B39" s="9"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="9"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="9"/>
-      <c r="H39" s="9"/>
-      <c r="I39" s="9"/>
-      <c r="J39" s="9"/>
-      <c r="K39" s="9"/>
-      <c r="L39" s="9"/>
-      <c r="M39" s="9"/>
-      <c r="N39" s="9"/>
-      <c r="O39" s="9"/>
+      <c r="B39" s="8"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="8"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="8"/>
+      <c r="G39" s="8"/>
+      <c r="H39" s="8"/>
+      <c r="I39" s="8"/>
+      <c r="J39" s="8"/>
+      <c r="K39" s="8"/>
+      <c r="L39" s="8"/>
+      <c r="M39" s="8"/>
+      <c r="N39" s="8"/>
+      <c r="O39" s="8"/>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A40" s="8" t="s">
+      <c r="A40" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="B40" s="9"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="9"/>
-      <c r="H40" s="9"/>
-      <c r="I40" s="9"/>
-      <c r="J40" s="9"/>
-      <c r="K40" s="9"/>
-      <c r="L40" s="9"/>
-      <c r="M40" s="9"/>
-      <c r="N40" s="9"/>
-      <c r="O40" s="9"/>
+      <c r="B40" s="8"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="8"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="8"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="8"/>
+      <c r="I40" s="8"/>
+      <c r="J40" s="8"/>
+      <c r="K40" s="8"/>
+      <c r="L40" s="8"/>
+      <c r="M40" s="8"/>
+      <c r="N40" s="8"/>
+      <c r="O40" s="8"/>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A41" s="8" t="s">
+      <c r="A41" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="B41" s="9"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="9"/>
-      <c r="H41" s="9"/>
-      <c r="I41" s="9"/>
-      <c r="J41" s="9"/>
-      <c r="K41" s="9"/>
-      <c r="L41" s="9"/>
-      <c r="M41" s="9"/>
-      <c r="N41" s="9"/>
-      <c r="O41" s="9"/>
+      <c r="B41" s="8"/>
+      <c r="C41" s="8"/>
+      <c r="D41" s="8"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="8"/>
+      <c r="G41" s="8"/>
+      <c r="H41" s="8"/>
+      <c r="I41" s="8"/>
+      <c r="J41" s="8"/>
+      <c r="K41" s="8"/>
+      <c r="L41" s="8"/>
+      <c r="M41" s="8"/>
+      <c r="N41" s="8"/>
+      <c r="O41" s="8"/>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A42" s="8" t="s">
+      <c r="A42" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="B42" s="9"/>
-      <c r="C42" s="9"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="9"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="9"/>
-      <c r="H42" s="9"/>
-      <c r="I42" s="9"/>
-      <c r="J42" s="9"/>
-      <c r="K42" s="9"/>
-      <c r="L42" s="9"/>
-      <c r="M42" s="9"/>
-      <c r="N42" s="9"/>
-      <c r="O42" s="9"/>
+      <c r="B42" s="8"/>
+      <c r="C42" s="8"/>
+      <c r="D42" s="8"/>
+      <c r="E42" s="8"/>
+      <c r="F42" s="8"/>
+      <c r="G42" s="8"/>
+      <c r="H42" s="8"/>
+      <c r="I42" s="8"/>
+      <c r="J42" s="8"/>
+      <c r="K42" s="8"/>
+      <c r="L42" s="8"/>
+      <c r="M42" s="8"/>
+      <c r="N42" s="8"/>
+      <c r="O42" s="8"/>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A43" s="8" t="s">
+      <c r="A43" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="B43" s="9"/>
-      <c r="C43" s="9"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="9"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="9"/>
-      <c r="H43" s="9"/>
-      <c r="I43" s="9"/>
-      <c r="J43" s="9"/>
-      <c r="K43" s="9"/>
-      <c r="L43" s="9"/>
-      <c r="M43" s="9"/>
-      <c r="N43" s="9"/>
-      <c r="O43" s="9"/>
+      <c r="B43" s="8"/>
+      <c r="C43" s="8"/>
+      <c r="D43" s="8"/>
+      <c r="E43" s="8"/>
+      <c r="F43" s="8"/>
+      <c r="G43" s="8"/>
+      <c r="H43" s="8"/>
+      <c r="I43" s="8"/>
+      <c r="J43" s="8"/>
+      <c r="K43" s="8"/>
+      <c r="L43" s="8"/>
+      <c r="M43" s="8"/>
+      <c r="N43" s="8"/>
+      <c r="O43" s="8"/>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A44" s="8" t="s">
+      <c r="A44" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="B44" s="9"/>
-      <c r="C44" s="9"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="9"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="9"/>
-      <c r="H44" s="9"/>
-      <c r="I44" s="9"/>
-      <c r="J44" s="9"/>
-      <c r="K44" s="9"/>
-      <c r="L44" s="9"/>
-      <c r="M44" s="9"/>
-      <c r="N44" s="9"/>
-      <c r="O44" s="9"/>
+      <c r="B44" s="8"/>
+      <c r="C44" s="8"/>
+      <c r="D44" s="8"/>
+      <c r="E44" s="8"/>
+      <c r="F44" s="8"/>
+      <c r="G44" s="8"/>
+      <c r="H44" s="8"/>
+      <c r="I44" s="8"/>
+      <c r="J44" s="8"/>
+      <c r="K44" s="8"/>
+      <c r="L44" s="8"/>
+      <c r="M44" s="8"/>
+      <c r="N44" s="8"/>
+      <c r="O44" s="8"/>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A45" s="8" t="s">
+      <c r="A45" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="B45" s="9"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="9"/>
-      <c r="E45" s="9"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="9"/>
-      <c r="H45" s="9"/>
-      <c r="I45" s="9"/>
-      <c r="J45" s="9"/>
-      <c r="K45" s="9"/>
-      <c r="L45" s="9"/>
-      <c r="M45" s="9"/>
-      <c r="N45" s="9"/>
-      <c r="O45" s="9"/>
+      <c r="B45" s="8"/>
+      <c r="C45" s="8"/>
+      <c r="D45" s="8"/>
+      <c r="E45" s="8"/>
+      <c r="F45" s="8"/>
+      <c r="G45" s="8"/>
+      <c r="H45" s="8"/>
+      <c r="I45" s="8"/>
+      <c r="J45" s="8"/>
+      <c r="K45" s="8"/>
+      <c r="L45" s="8"/>
+      <c r="M45" s="8"/>
+      <c r="N45" s="8"/>
+      <c r="O45" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -5361,678 +5463,678 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="10" t="s">
         <v>213</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="J4" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="K4" s="11" t="s">
+      <c r="K4" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="L4" s="11" t="s">
+      <c r="L4" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="M4" s="11" t="s">
+      <c r="M4" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="N4" s="11" t="s">
+      <c r="N4" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="O4" s="11" t="s">
+      <c r="O4" s="10" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="14" t="s">
         <v>219</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="14" t="s">
         <v>220</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="14" t="s">
         <v>221</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="14" t="s">
         <v>222</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="I5" s="14" t="s">
         <v>223</v>
       </c>
-      <c r="J5" s="15" t="s">
+      <c r="J5" s="14" t="s">
         <v>224</v>
       </c>
-      <c r="K5" s="15" t="s">
+      <c r="K5" s="14" t="s">
         <v>225</v>
       </c>
-      <c r="L5" s="15" t="s">
+      <c r="L5" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="M5" s="15" t="s">
+      <c r="M5" s="14" t="s">
         <v>227</v>
       </c>
-      <c r="N5" s="15" t="s">
+      <c r="N5" s="14" t="s">
         <v>228</v>
       </c>
-      <c r="O5" s="15" t="s">
+      <c r="O5" s="14" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
-      <c r="L6" s="9"/>
-      <c r="M6" s="9"/>
-      <c r="N6" s="9"/>
-      <c r="O6" s="9"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="8"/>
+      <c r="N6" s="8"/>
+      <c r="O6" s="8"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9"/>
-      <c r="N7" s="9"/>
-      <c r="O7" s="9"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="9"/>
-      <c r="M8" s="9"/>
-      <c r="N8" s="9"/>
-      <c r="O8" s="9"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
-      <c r="N9" s="9"/>
-      <c r="O9" s="9"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="8"/>
+      <c r="O9" s="8"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="9"/>
-      <c r="L10" s="9"/>
-      <c r="M10" s="9"/>
-      <c r="N10" s="9"/>
-      <c r="O10" s="9"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>235</v>
       </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
-      <c r="L11" s="9"/>
-      <c r="M11" s="9"/>
-      <c r="N11" s="9"/>
-      <c r="O11" s="9"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="8"/>
+      <c r="O11" s="8"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="9"/>
-      <c r="M12" s="9"/>
-      <c r="N12" s="9"/>
-      <c r="O12" s="9"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="7" t="s">
         <v>237</v>
       </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="9"/>
-      <c r="M13" s="9"/>
-      <c r="N13" s="9"/>
-      <c r="O13" s="9"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="8"/>
+      <c r="N13" s="8"/>
+      <c r="O13" s="8"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="7" t="s">
         <v>238</v>
       </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="9"/>
-      <c r="N14" s="9"/>
-      <c r="O14" s="9"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="8"/>
+      <c r="O14" s="8"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
-      <c r="K15" s="9"/>
-      <c r="L15" s="9"/>
-      <c r="M15" s="9"/>
-      <c r="N15" s="9"/>
-      <c r="O15" s="9"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="8"/>
+      <c r="N15" s="8"/>
+      <c r="O15" s="8"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
-      <c r="K16" s="9"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="9"/>
-      <c r="O16" s="9"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="8"/>
+      <c r="O16" s="8"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="7" t="s">
         <v>241</v>
       </c>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
-      <c r="K17" s="9"/>
-      <c r="L17" s="9"/>
-      <c r="M17" s="9"/>
-      <c r="N17" s="9"/>
-      <c r="O17" s="9"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="8"/>
+      <c r="N17" s="8"/>
+      <c r="O17" s="8"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
-      <c r="M18" s="9"/>
-      <c r="N18" s="9"/>
-      <c r="O18" s="9"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="8"/>
+      <c r="N18" s="8"/>
+      <c r="O18" s="8"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
-      <c r="K19" s="9"/>
-      <c r="L19" s="9"/>
-      <c r="M19" s="9"/>
-      <c r="N19" s="9"/>
-      <c r="O19" s="9"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="8"/>
+      <c r="M19" s="8"/>
+      <c r="N19" s="8"/>
+      <c r="O19" s="8"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="7" t="s">
         <v>244</v>
       </c>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
-      <c r="K20" s="9"/>
-      <c r="L20" s="9"/>
-      <c r="M20" s="9"/>
-      <c r="N20" s="9"/>
-      <c r="O20" s="9"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="8"/>
+      <c r="N20" s="8"/>
+      <c r="O20" s="8"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="7" t="s">
         <v>245</v>
       </c>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="9"/>
-      <c r="K21" s="9"/>
-      <c r="L21" s="9"/>
-      <c r="M21" s="9"/>
-      <c r="N21" s="9"/>
-      <c r="O21" s="9"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="8"/>
+      <c r="N21" s="8"/>
+      <c r="O21" s="8"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="9"/>
-      <c r="K22" s="9"/>
-      <c r="L22" s="9"/>
-      <c r="M22" s="9"/>
-      <c r="N22" s="9"/>
-      <c r="O22" s="9"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="8"/>
+      <c r="N22" s="8"/>
+      <c r="O22" s="8"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="7" t="s">
         <v>247</v>
       </c>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="9"/>
-      <c r="K23" s="9"/>
-      <c r="L23" s="9"/>
-      <c r="M23" s="9"/>
-      <c r="N23" s="9"/>
-      <c r="O23" s="9"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="8"/>
+      <c r="N23" s="8"/>
+      <c r="O23" s="8"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="9"/>
-      <c r="K24" s="9"/>
-      <c r="L24" s="9"/>
-      <c r="M24" s="9"/>
-      <c r="N24" s="9"/>
-      <c r="O24" s="9"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+      <c r="N24" s="8"/>
+      <c r="O24" s="8"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="9"/>
-      <c r="K25" s="9"/>
-      <c r="L25" s="9"/>
-      <c r="M25" s="9"/>
-      <c r="N25" s="9"/>
-      <c r="O25" s="9"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="8"/>
+      <c r="K25" s="8"/>
+      <c r="L25" s="8"/>
+      <c r="M25" s="8"/>
+      <c r="N25" s="8"/>
+      <c r="O25" s="8"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="9"/>
-      <c r="J26" s="9"/>
-      <c r="K26" s="9"/>
-      <c r="L26" s="9"/>
-      <c r="M26" s="9"/>
-      <c r="N26" s="9"/>
-      <c r="O26" s="9"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="8"/>
+      <c r="K26" s="8"/>
+      <c r="L26" s="8"/>
+      <c r="M26" s="8"/>
+      <c r="N26" s="8"/>
+      <c r="O26" s="8"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="7" t="s">
         <v>251</v>
       </c>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="9"/>
-      <c r="J27" s="9"/>
-      <c r="K27" s="9"/>
-      <c r="L27" s="9"/>
-      <c r="M27" s="9"/>
-      <c r="N27" s="9"/>
-      <c r="O27" s="9"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
+      <c r="J27" s="8"/>
+      <c r="K27" s="8"/>
+      <c r="L27" s="8"/>
+      <c r="M27" s="8"/>
+      <c r="N27" s="8"/>
+      <c r="O27" s="8"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
-      <c r="J28" s="9"/>
-      <c r="K28" s="9"/>
-      <c r="L28" s="9"/>
-      <c r="M28" s="9"/>
-      <c r="N28" s="9"/>
-      <c r="O28" s="9"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8"/>
+      <c r="J28" s="8"/>
+      <c r="K28" s="8"/>
+      <c r="L28" s="8"/>
+      <c r="M28" s="8"/>
+      <c r="N28" s="8"/>
+      <c r="O28" s="8"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="9"/>
-      <c r="J29" s="9"/>
-      <c r="K29" s="9"/>
-      <c r="L29" s="9"/>
-      <c r="M29" s="9"/>
-      <c r="N29" s="9"/>
-      <c r="O29" s="9"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="8"/>
+      <c r="J29" s="8"/>
+      <c r="K29" s="8"/>
+      <c r="L29" s="8"/>
+      <c r="M29" s="8"/>
+      <c r="N29" s="8"/>
+      <c r="O29" s="8"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A30" s="8" t="s">
+      <c r="A30" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="9"/>
-      <c r="J30" s="9"/>
-      <c r="K30" s="9"/>
-      <c r="L30" s="9"/>
-      <c r="M30" s="9"/>
-      <c r="N30" s="9"/>
-      <c r="O30" s="9"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="8"/>
+      <c r="J30" s="8"/>
+      <c r="K30" s="8"/>
+      <c r="L30" s="8"/>
+      <c r="M30" s="8"/>
+      <c r="N30" s="8"/>
+      <c r="O30" s="8"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="7" t="s">
         <v>255</v>
       </c>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="9"/>
-      <c r="J31" s="9"/>
-      <c r="K31" s="9"/>
-      <c r="L31" s="9"/>
-      <c r="M31" s="9"/>
-      <c r="N31" s="9"/>
-      <c r="O31" s="9"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="8"/>
+      <c r="I31" s="8"/>
+      <c r="J31" s="8"/>
+      <c r="K31" s="8"/>
+      <c r="L31" s="8"/>
+      <c r="M31" s="8"/>
+      <c r="N31" s="8"/>
+      <c r="O31" s="8"/>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="9"/>
-      <c r="J32" s="9"/>
-      <c r="K32" s="9"/>
-      <c r="L32" s="9"/>
-      <c r="M32" s="9"/>
-      <c r="N32" s="9"/>
-      <c r="O32" s="9"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="8"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="8"/>
+      <c r="I32" s="8"/>
+      <c r="J32" s="8"/>
+      <c r="K32" s="8"/>
+      <c r="L32" s="8"/>
+      <c r="M32" s="8"/>
+      <c r="N32" s="8"/>
+      <c r="O32" s="8"/>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="9"/>
-      <c r="J33" s="9"/>
-      <c r="K33" s="9"/>
-      <c r="L33" s="9"/>
-      <c r="M33" s="9"/>
-      <c r="N33" s="9"/>
-      <c r="O33" s="9"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="8"/>
+      <c r="I33" s="8"/>
+      <c r="J33" s="8"/>
+      <c r="K33" s="8"/>
+      <c r="L33" s="8"/>
+      <c r="M33" s="8"/>
+      <c r="N33" s="8"/>
+      <c r="O33" s="8"/>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A34" s="8" t="s">
+      <c r="A34" s="7" t="s">
         <v>258</v>
       </c>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="9"/>
-      <c r="J34" s="9"/>
-      <c r="K34" s="9"/>
-      <c r="L34" s="9"/>
-      <c r="M34" s="9"/>
-      <c r="N34" s="9"/>
-      <c r="O34" s="9"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="8"/>
+      <c r="I34" s="8"/>
+      <c r="J34" s="8"/>
+      <c r="K34" s="8"/>
+      <c r="L34" s="8"/>
+      <c r="M34" s="8"/>
+      <c r="N34" s="8"/>
+      <c r="O34" s="8"/>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A35" s="8" t="s">
+      <c r="A35" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="9"/>
-      <c r="I35" s="9"/>
-      <c r="J35" s="9"/>
-      <c r="K35" s="9"/>
-      <c r="L35" s="9"/>
-      <c r="M35" s="9"/>
-      <c r="N35" s="9"/>
-      <c r="O35" s="9"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="8"/>
+      <c r="I35" s="8"/>
+      <c r="J35" s="8"/>
+      <c r="K35" s="8"/>
+      <c r="L35" s="8"/>
+      <c r="M35" s="8"/>
+      <c r="N35" s="8"/>
+      <c r="O35" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -6118,300 +6220,300 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="10" t="s">
         <v>263</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="10" t="s">
         <v>264</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="10" t="s">
         <v>265</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="J4" s="10" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="14" t="s">
         <v>266</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="14" t="s">
         <v>267</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="14" t="s">
         <v>268</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="14" t="s">
         <v>269</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="14" t="s">
         <v>270</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="14" t="s">
         <v>271</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="I5" s="15"/>
-      <c r="J5" s="15" t="s">
+      <c r="I5" s="14"/>
+      <c r="J5" s="14" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>275</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>276</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>277</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>278</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="7" t="s">
         <v>279</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="7" t="s">
         <v>280</v>
       </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="7" t="s">
         <v>281</v>
       </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="7" t="s">
         <v>282</v>
       </c>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="7" t="s">
         <v>283</v>
       </c>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="7" t="s">
         <v>284</v>
       </c>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="7" t="s">
         <v>285</v>
       </c>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="7" t="s">
         <v>287</v>
       </c>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -6470,356 +6572,356 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>291</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="10" t="s">
         <v>292</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="10" t="s">
         <v>294</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="J4" s="10" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="14" t="s">
         <v>295</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="14" t="s">
         <v>296</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="14" t="s">
         <v>297</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="14" t="s">
         <v>298</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="14" t="s">
         <v>299</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="14" t="s">
         <v>300</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="14" t="s">
         <v>301</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="I5" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="J5" s="15"/>
+      <c r="J5" s="14"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>302</v>
       </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>303</v>
       </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>305</v>
       </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>306</v>
       </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>307</v>
       </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="7" t="s">
         <v>308</v>
       </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="7" t="s">
         <v>309</v>
       </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="7" t="s">
         <v>310</v>
       </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="7" t="s">
         <v>311</v>
       </c>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="7" t="s">
         <v>312</v>
       </c>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="7" t="s">
         <v>313</v>
       </c>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="7" t="s">
         <v>314</v>
       </c>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="7" t="s">
         <v>315</v>
       </c>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="7" t="s">
         <v>316</v>
       </c>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="9"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="7" t="s">
         <v>318</v>
       </c>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="9"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="7" t="s">
         <v>319</v>
       </c>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="9"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="7" t="s">
         <v>320</v>
       </c>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="9"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="7" t="s">
         <v>321</v>
       </c>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="9"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/relatorio/Relatorio_de_Testes_CineLume.xlsx
+++ b/relatorio/Relatorio_de_Testes_CineLume.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aluno\Documents\GitHub\cinelume-qa\relatorio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BE178D8-F95E-4838-A6CA-C1F7F1910C8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{971E39B6-7A20-4D00-9FA7-B047963AE2C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0_Instrucoes" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="528">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="821" uniqueCount="606">
   <si>
     <t>Relatório de Testes — CineLume v1.0</t>
   </si>
@@ -485,9 +485,6 @@
   </si>
   <si>
     <t>Aceitação</t>
-  </si>
-  <si>
-    <t>5. Casos de teste (Missões 2 e 3)</t>
   </si>
   <si>
     <t>M2: preencha as colunas B a K (projeto do caso). M3: execute e preencha L a O. Mínimo: 15 casos, pelo menos 5 de valor limite.</t>
@@ -1638,6 +1635,243 @@
   </si>
   <si>
     <t>validar quantidade de meia entrada por assentos,executar aplicação do cupom,testa o fluxo do botao de corfimação da compra, testa de restrição de idade</t>
+  </si>
+  <si>
+    <t>Testar o sistema em um celular , Testar a integração com o gateway real de pagamento de um banco ,Testar a segurança contra ataques de invasão</t>
+  </si>
+  <si>
+    <t>usamos testes funcionais , por que permite uma validação e execução por meio de fluxos de ponta a ponta</t>
+  </si>
+  <si>
+    <t>unitários,aceitação ,integração</t>
+  </si>
+  <si>
+    <t>Ánalise de valor limite ,participação equivalência</t>
+  </si>
+  <si>
+    <t>vscode,sistema ,devtools</t>
+  </si>
+  <si>
+    <t>Pelo menos 90% dos casos de teste executados tiverem passado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">correção dos bugs </t>
+  </si>
+  <si>
+    <t>5. Casos de teste (Missões 2 e 3)+A1:I12</t>
+  </si>
+  <si>
+    <t>acesse o navegador, escolha a sessão , escolhar 1 assento</t>
+  </si>
+  <si>
+    <t>que o desconto seja aplicado so no ingresso</t>
+  </si>
+  <si>
+    <t>na Aplicação da Taxa de Conveniência com o Cupom CINE10</t>
+  </si>
+  <si>
+    <t>o desconto ate sendo aplicado com o valor total</t>
+  </si>
+  <si>
+    <t>uso do cumpom :cine10</t>
+  </si>
+  <si>
+    <t>use o desconto</t>
+  </si>
+  <si>
+    <t>CA14.4</t>
+  </si>
+  <si>
+    <t>CA15.5</t>
+  </si>
+  <si>
+    <t>uso de email muito simples</t>
+  </si>
+  <si>
+    <t>acesse o navegador, escolha a sessão , informe o dados pessoais</t>
+  </si>
+  <si>
+    <t>email: vc@gmail.com</t>
+  </si>
+  <si>
+    <t>email não tem quantidade certa de caractere</t>
+  </si>
+  <si>
+    <t>preenchimento de dados pessoais</t>
+  </si>
+  <si>
+    <t>Validação do limite mínimo de idade para sessões maiores de 18 anos</t>
+  </si>
+  <si>
+    <t>Usuário na tela de cadastro ou seleção de filme restrito</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Inserir a data de nascimento correspondente a 17 anos e 364 dias; Tentar avançar para a compra</t>
+  </si>
+  <si>
+    <t>Data de nascimento: (Idade &lt; 18 anos)</t>
+  </si>
+  <si>
+    <t>uso do cumpom</t>
+  </si>
+  <si>
+    <t>CA 16.6</t>
+  </si>
+  <si>
+    <t>Não tem opção</t>
+  </si>
+  <si>
+    <t>O sistema deve bloquear o acesso à sessão e exibir alerta de restrição de idade.</t>
+  </si>
+  <si>
+    <t>O sistema não esta exigindo idade</t>
+  </si>
+  <si>
+    <t>CA17.7</t>
+  </si>
+  <si>
+    <t>Fazer a finalização da compra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">escolha a sessão, Preenchar os dados , finalize a comprar </t>
+  </si>
+  <si>
+    <t>preenche os dados</t>
+  </si>
+  <si>
+    <t>o botão deve fica bloqueado durante o pagamento</t>
+  </si>
+  <si>
+    <t>o botão esta livre para clicar varias vezes</t>
+  </si>
+  <si>
+    <t>clique varias vezes no botão</t>
+  </si>
+  <si>
+    <t>CA18.8</t>
+  </si>
+  <si>
+    <t>escolha o pix ou o cartão para fazer comprar</t>
+  </si>
+  <si>
+    <t>escolha a sessão, Preenchar os dados ,escolha forma de pagamento</t>
+  </si>
+  <si>
+    <t>forma de pagamento</t>
+  </si>
+  <si>
+    <t>o valor total não pode ser alterado ao escolha forma de pagamento</t>
+  </si>
+  <si>
+    <t>o valor diminui a cada escolha da forma de pagamento</t>
+  </si>
+  <si>
+    <t>fique alternado entre a forma de pagamento</t>
+  </si>
+  <si>
+    <t>Escolha a sessão e saia dela</t>
+  </si>
+  <si>
+    <t>acesse o navegador , escolha a sessão , sair da sessão</t>
+  </si>
+  <si>
+    <t>ao sair da sessão o assento escolhido ser reiniciado</t>
+  </si>
+  <si>
+    <t>ao escolhe o assento fica como se tivesse comprado ou não</t>
+  </si>
+  <si>
+    <t>escolha o assento e saia da sessão</t>
+  </si>
+  <si>
+    <t>Aplicação do cumpom cine10</t>
+  </si>
+  <si>
+    <t>ct-01</t>
+  </si>
+  <si>
+    <t>ct-02</t>
+  </si>
+  <si>
+    <t>ct-03</t>
+  </si>
+  <si>
+    <t>ct-04</t>
+  </si>
+  <si>
+    <t>ct-05</t>
+  </si>
+  <si>
+    <t>ct-06</t>
+  </si>
+  <si>
+    <t>escolha o assento , digite o cumpom, clique em aplicar</t>
+  </si>
+  <si>
+    <t>desconto no ingresso</t>
+  </si>
+  <si>
+    <t>desconto no subtotal da compra</t>
+  </si>
+  <si>
+    <t>escolha a sessao, preenchar os dados</t>
+  </si>
+  <si>
+    <t>ter if e else para diferencia um email simples</t>
+  </si>
+  <si>
+    <t>qualquer email pode ser usado</t>
+  </si>
+  <si>
+    <t>conflito Dinâmico no Desconto Pix com Cupons e Taxas</t>
+  </si>
+  <si>
+    <t>escolha de pagamento</t>
+  </si>
+  <si>
+    <t>uso do email</t>
+  </si>
+  <si>
+    <t>adicone o cumpom</t>
+  </si>
+  <si>
+    <t>o valor total não subtrai com nenhum desconto  de pagamento</t>
+  </si>
+  <si>
+    <t>ele dimuiniu a cada alteração de pagamento</t>
+  </si>
+  <si>
+    <t>CA19.9</t>
+  </si>
+  <si>
+    <t>CA 19.9</t>
+  </si>
+  <si>
+    <t>acesse a sessão escolha o assento e saia dela</t>
+  </si>
+  <si>
+    <t>ao sair da sessão que escolheu o assento que o site renicie</t>
+  </si>
+  <si>
+    <t>dados pessoais</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fica como se tivesse comprado  </t>
+  </si>
+  <si>
+    <t>o botão de confirma bloqueado durante processo</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> o botão fica acessivel</t>
+  </si>
+  <si>
+    <t>preenche datas de nascimento</t>
+  </si>
+  <si>
+    <t>ter os dados de nascimento</t>
+  </si>
+  <si>
+    <t>não tem</t>
   </si>
 </sst>
 </file>
@@ -1783,7 +2017,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -1827,6 +2061,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2327,12 +2564,12 @@
   <sheetData>
     <row r="1" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -2340,60 +2577,60 @@
         <v>64</v>
       </c>
       <c r="B4" s="10" t="s">
+        <v>323</v>
+      </c>
+      <c r="C4" s="10" t="s">
         <v>324</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>325</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>88</v>
       </c>
       <c r="E4" s="10" t="s">
+        <v>325</v>
+      </c>
+      <c r="F4" s="10" t="s">
         <v>326</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="G4" s="10" t="s">
         <v>327</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="H4" s="10" t="s">
         <v>328</v>
       </c>
-      <c r="H4" s="10" t="s">
-        <v>329</v>
-      </c>
       <c r="I4" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
+        <v>329</v>
+      </c>
+      <c r="B5" s="14" t="s">
         <v>330</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="C5" s="14" t="s">
         <v>331</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>332</v>
       </c>
       <c r="D5" s="14" t="s">
         <v>94</v>
       </c>
       <c r="E5" s="14" t="s">
+        <v>332</v>
+      </c>
+      <c r="F5" s="14" t="s">
         <v>333</v>
       </c>
-      <c r="F5" s="14" t="s">
-        <v>334</v>
-      </c>
       <c r="G5" s="14" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I5" s="14"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -2406,7 +2643,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
@@ -2419,7 +2656,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
@@ -2432,7 +2669,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
@@ -2445,7 +2682,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
@@ -2458,7 +2695,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
@@ -2471,7 +2708,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
@@ -2484,7 +2721,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -2497,7 +2734,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -2510,7 +2747,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
@@ -2523,7 +2760,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
@@ -2536,7 +2773,7 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
@@ -2549,7 +2786,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
@@ -2562,7 +2799,7 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
@@ -2575,7 +2812,7 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
@@ -2588,7 +2825,7 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
@@ -2601,7 +2838,7 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
@@ -2614,7 +2851,7 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
@@ -2627,7 +2864,7 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
@@ -2640,7 +2877,7 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
@@ -2709,12 +2946,12 @@
   <sheetData>
     <row r="1" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -2722,42 +2959,42 @@
         <v>64</v>
       </c>
       <c r="B4" s="10" t="s">
+        <v>356</v>
+      </c>
+      <c r="C4" s="10" t="s">
         <v>357</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="D4" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="E4" s="10" t="s">
         <v>358</v>
       </c>
-      <c r="D4" s="10" t="s">
-        <v>290</v>
-      </c>
-      <c r="E4" s="10" t="s">
+      <c r="F4" s="10" t="s">
         <v>359</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="G4" s="10" t="s">
         <v>360</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="H4" s="10" t="s">
         <v>361</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="I4" s="10" t="s">
         <v>362</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="J4" s="10" t="s">
         <v>363</v>
       </c>
-      <c r="J4" s="10" t="s">
+      <c r="K4" s="10" t="s">
         <v>364</v>
       </c>
-      <c r="K4" s="10" t="s">
+      <c r="L4" s="10" t="s">
         <v>365</v>
-      </c>
-      <c r="L4" s="10" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -2773,7 +3010,7 @@
     </row>
     <row r="6" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -2789,7 +3026,7 @@
     </row>
     <row r="7" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
@@ -2845,32 +3082,32 @@
   <sheetData>
     <row r="1" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B4" s="16"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B5" s="18">
         <f>COUNTA('5_Casos_de_Teste'!G6:G45)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B6" s="18">
         <f>COUNTIF('5_Casos_de_Teste'!M6:M45,"Passou")</f>
@@ -2879,16 +3116,16 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B7" s="18">
         <f>COUNTIF('5_Casos_de_Teste'!M6:M45,"Falhou")</f>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B8" s="18">
         <f>COUNTIF('5_Casos_de_Teste'!M6:M45,"Bloqueado")</f>
@@ -2897,16 +3134,16 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="17" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B9" s="18">
         <f>COUNTIF('5_Casos_de_Teste'!M6:M45,"Não executado")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="17" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B10" s="19">
         <f>IFERROR(B6/(B6+B7+B8),0)</f>
@@ -2915,61 +3152,61 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B11" s="18">
         <f>COUNTIF('5_Casos_de_Teste'!D6:D45,"Valor limite")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B12" s="18">
         <f>COUNTA('6_Bugs'!B6:B35)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="17" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B13" s="18">
         <f>COUNTIF('6_Bugs'!G6:G35,"Crítica")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="17" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B14" s="18">
         <f>COUNTIF('6_Bugs'!G6:G35,"Alta")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B15" s="18">
         <f>COUNTIF('6_Bugs'!G6:G35,"Média")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="17" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B16" s="18">
         <f>COUNTIF('6_Bugs'!G6:G35,"Baixa")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="17" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B17" s="18">
         <f>COUNTIF('6_Bugs'!N6:N35,"Corrigido*")</f>
@@ -2978,7 +3215,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="17" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B18" s="18">
         <f>COUNTA('7_Nao_Funcionais'!H6:H20)</f>
@@ -2987,7 +3224,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="17" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B19" s="18">
         <f>COUNTIF('7_Nao_Funcionais'!H6:H20,"Falhou")</f>
@@ -2996,7 +3233,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B20" s="18">
         <f>COUNTA('8_Caixa_Branca'!C6:C25)</f>
@@ -3005,7 +3242,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="17" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B21" s="18">
         <f>COUNTA('9_Automacao'!E6:E25)</f>
@@ -3014,7 +3251,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="17" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B22" s="18">
         <f>COUNTIF('9_Automacao'!H6:H25,"Passou")</f>
@@ -3023,7 +3260,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="17" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B23" s="18">
         <f>COUNTIF('9_Automacao'!H6:H25,"Falhou")</f>
@@ -3032,72 +3269,72 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="15" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B25" s="16"/>
       <c r="C25" s="16"/>
     </row>
     <row r="26" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B26" s="22"/>
       <c r="C26" s="22"/>
       <c r="D26" s="9" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B27" s="22"/>
       <c r="C27" s="22"/>
     </row>
     <row r="28" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B28" s="22"/>
       <c r="C28" s="22"/>
     </row>
     <row r="29" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B29" s="22"/>
       <c r="C29" s="22"/>
     </row>
     <row r="30" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B30" s="22"/>
       <c r="C30" s="22"/>
       <c r="D30" s="9" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B31" s="22"/>
       <c r="C31" s="22"/>
       <c r="D31" s="9" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B32" s="22"/>
       <c r="C32" s="22"/>
     </row>
     <row r="33" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B33" s="22"/>
       <c r="C33" s="22"/>
@@ -3149,12 +3386,12 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3162,27 +3399,27 @@
         <v>64</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C4" s="10" t="s">
+        <v>405</v>
+      </c>
+      <c r="D4" s="10" t="s">
         <v>406</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="E4" s="10" t="s">
         <v>407</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="F4" s="10" t="s">
         <v>408</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="G4" s="10" t="s">
         <v>409</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -3193,7 +3430,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -3204,7 +3441,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
@@ -3215,7 +3452,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
@@ -3226,7 +3463,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
@@ -3237,7 +3474,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
@@ -3248,7 +3485,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
@@ -3259,7 +3496,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
@@ -3270,7 +3507,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -3281,7 +3518,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -3321,66 +3558,66 @@
         <v>88</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>421</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>422</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>423</v>
-      </c>
       <c r="E1" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>38</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H1" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="I1" s="5" t="s">
         <v>424</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>425</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>426</v>
       </c>
       <c r="K1" s="5" t="s">
         <v>84</v>
       </c>
       <c r="L1" s="5" t="s">
+        <v>426</v>
+      </c>
+      <c r="M1" s="5" t="s">
         <v>427</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>428</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>429</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="P1" s="5" t="s">
         <v>430</v>
-      </c>
-      <c r="P1" s="5" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>133</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>39</v>
@@ -3389,48 +3626,48 @@
         <v>41</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I2" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="J2" s="6" t="s">
         <v>434</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="K2" s="6" t="s">
         <v>435</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="L2" s="6" t="s">
         <v>436</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="M2" s="6" t="s">
         <v>437</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="N2" s="6" t="s">
         <v>438</v>
       </c>
-      <c r="N2" s="6" t="s">
+      <c r="O2" s="6" t="s">
         <v>439</v>
       </c>
-      <c r="O2" s="6" t="s">
+      <c r="P2" s="6" t="s">
         <v>440</v>
-      </c>
-      <c r="P2" s="6" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
+        <v>441</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>442</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>443</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>144</v>
       </c>
       <c r="D3" s="6" t="s">
+        <v>443</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>444</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>445</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>41</v>
@@ -3439,48 +3676,48 @@
         <v>43</v>
       </c>
       <c r="H3" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="I3" s="6" t="s">
         <v>446</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="J3" s="6" t="s">
+        <v>444</v>
+      </c>
+      <c r="K3" s="6" t="s">
         <v>447</v>
       </c>
-      <c r="J3" s="6" t="s">
-        <v>445</v>
-      </c>
-      <c r="K3" s="6" t="s">
+      <c r="L3" s="6" t="s">
         <v>448</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="M3" s="6" t="s">
         <v>449</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="N3" s="6" t="s">
         <v>450</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>451</v>
       </c>
       <c r="O3" s="6" t="s">
         <v>96</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
+        <v>452</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>453</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>454</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>134</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>43</v>
@@ -3489,30 +3726,30 @@
         <v>45</v>
       </c>
       <c r="H4" s="6" t="s">
+        <v>455</v>
+      </c>
+      <c r="L4" s="6" t="s">
         <v>456</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="M4" s="6" t="s">
         <v>457</v>
       </c>
-      <c r="M4" s="6" t="s">
+      <c r="N4" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="O4" s="6" t="s">
         <v>458</v>
       </c>
-      <c r="N4" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="O4" s="6" t="s">
+      <c r="P4" s="6" t="s">
         <v>459</v>
-      </c>
-      <c r="P4" s="6" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
+        <v>460</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>461</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>462</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>135</v>
@@ -3521,125 +3758,125 @@
         <v>144</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>45</v>
       </c>
       <c r="H5" s="6" t="s">
+        <v>463</v>
+      </c>
+      <c r="M5" s="6" t="s">
         <v>464</v>
       </c>
-      <c r="M5" s="6" t="s">
+      <c r="N5" s="6" t="s">
         <v>465</v>
       </c>
-      <c r="N5" s="6" t="s">
+      <c r="O5" s="6" t="s">
         <v>466</v>
-      </c>
-      <c r="O5" s="6" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>136</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="M6" s="6" t="s">
+        <v>468</v>
+      </c>
+      <c r="N6" s="6" t="s">
         <v>469</v>
-      </c>
-      <c r="N6" s="6" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
+        <v>470</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>471</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>472</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>136</v>
       </c>
       <c r="M7" s="6" t="s">
+        <v>472</v>
+      </c>
+      <c r="N7" s="6" t="s">
         <v>473</v>
-      </c>
-      <c r="N7" s="6" t="s">
-        <v>474</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
+        <v>474</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>475</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>476</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>137</v>
       </c>
       <c r="M8" s="6" t="s">
+        <v>476</v>
+      </c>
+      <c r="N8" s="6" t="s">
         <v>477</v>
-      </c>
-      <c r="N8" s="6" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
+        <v>478</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>479</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>480</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>138</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>139</v>
       </c>
       <c r="M10" s="6" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>140</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>141</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>142</v>
@@ -3655,45 +3892,45 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="C15" s="6" t="s">
         <v>486</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
   </sheetData>
@@ -3836,7 +4073,7 @@
         <v>69</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D5" s="8"/>
     </row>
@@ -3848,7 +4085,7 @@
         <v>71</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D6" s="8"/>
     </row>
@@ -3860,7 +4097,7 @@
         <v>73</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D7" s="8"/>
     </row>
@@ -3872,7 +4109,7 @@
         <v>75</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D8" s="8"/>
     </row>
@@ -3884,7 +4121,7 @@
         <v>77</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D9" s="8"/>
     </row>
@@ -3896,7 +4133,7 @@
         <v>79</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D10" s="8"/>
     </row>
@@ -3908,7 +4145,7 @@
         <v>81</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D11" s="8"/>
     </row>
@@ -3920,7 +4157,7 @@
         <v>83</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D12" s="8"/>
     </row>
@@ -3929,7 +4166,7 @@
         <v>84</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
@@ -4035,19 +4272,19 @@
         <v>99</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>96</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="66" x14ac:dyDescent="0.3">
@@ -4055,19 +4292,19 @@
         <v>100</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="92.4" x14ac:dyDescent="0.3">
@@ -4075,19 +4312,19 @@
         <v>101</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>96</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="92.4" x14ac:dyDescent="0.3">
@@ -4095,19 +4332,19 @@
         <v>102</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C9" s="21" t="s">
+        <v>500</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>466</v>
+      </c>
+      <c r="E9" s="21" t="s">
         <v>501</v>
       </c>
-      <c r="D9" s="8" t="s">
-        <v>467</v>
-      </c>
-      <c r="E9" s="21" t="s">
-        <v>502</v>
-      </c>
       <c r="F9" s="8" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="92.4" x14ac:dyDescent="0.3">
@@ -4115,19 +4352,19 @@
         <v>103</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>96</v>
       </c>
       <c r="E10" s="21" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="66" x14ac:dyDescent="0.3">
@@ -4138,16 +4375,16 @@
         <v>94</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E11" s="21" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="79.2" x14ac:dyDescent="0.3">
@@ -4155,19 +4392,19 @@
         <v>105</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>96</v>
       </c>
       <c r="E12" s="21" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="92.4" x14ac:dyDescent="0.3">
@@ -4175,19 +4412,19 @@
         <v>106</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>96</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="79.2" x14ac:dyDescent="0.3">
@@ -4195,19 +4432,19 @@
         <v>107</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>96</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="105.6" x14ac:dyDescent="0.3">
@@ -4215,19 +4452,19 @@
         <v>108</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E15" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="F15" s="8" t="s">
         <v>514</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>515</v>
       </c>
     </row>
   </sheetData>
@@ -4272,7 +4509,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -4285,7 +4522,7 @@
         <v>110</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
@@ -4293,7 +4530,7 @@
         <v>111</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>112</v>
@@ -4303,13 +4540,17 @@
       <c r="A6" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="B6" s="8"/>
+      <c r="B6" s="8" t="s">
+        <v>527</v>
+      </c>
     </row>
     <row r="7" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="B7" s="8"/>
+      <c r="B7" s="8" t="s">
+        <v>451</v>
+      </c>
       <c r="C7" s="9" t="s">
         <v>115</v>
       </c>
@@ -4318,13 +4559,17 @@
       <c r="A8" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="B8" s="8"/>
+      <c r="B8" s="8" t="s">
+        <v>528</v>
+      </c>
     </row>
     <row r="9" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="B9" s="8"/>
+      <c r="B9" s="8" t="s">
+        <v>529</v>
+      </c>
       <c r="C9" s="9" t="s">
         <v>118</v>
       </c>
@@ -4333,7 +4578,9 @@
       <c r="A10" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="B10" s="8"/>
+      <c r="B10" s="8" t="s">
+        <v>530</v>
+      </c>
       <c r="C10" s="9" t="s">
         <v>120</v>
       </c>
@@ -4342,7 +4589,9 @@
       <c r="A11" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="B11" s="8"/>
+      <c r="B11" s="8" t="s">
+        <v>531</v>
+      </c>
       <c r="C11" s="9" t="s">
         <v>122</v>
       </c>
@@ -4351,7 +4600,9 @@
       <c r="A12" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="B12" s="8"/>
+      <c r="B12" s="23">
+        <v>0.77083333333333337</v>
+      </c>
       <c r="C12" s="9" t="s">
         <v>124</v>
       </c>
@@ -4360,7 +4611,9 @@
       <c r="A13" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="B13" s="8"/>
+      <c r="B13" s="8" t="s">
+        <v>532</v>
+      </c>
       <c r="C13" s="9" t="s">
         <v>126</v>
       </c>
@@ -4369,7 +4622,9 @@
       <c r="A14" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="B14" s="8"/>
+      <c r="B14" s="8" t="s">
+        <v>533</v>
+      </c>
       <c r="C14" s="9" t="s">
         <v>128</v>
       </c>
@@ -4394,84 +4649,108 @@
       <c r="A19" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="B19" s="8"/>
+      <c r="B19" s="8" t="s">
+        <v>433</v>
+      </c>
       <c r="C19" s="8"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="B20" s="8"/>
+      <c r="B20" s="8" t="s">
+        <v>433</v>
+      </c>
       <c r="C20" s="8"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="B21" s="8"/>
+      <c r="B21" s="8" t="s">
+        <v>433</v>
+      </c>
       <c r="C21" s="8"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="B22" s="8"/>
+      <c r="B22" s="8" t="s">
+        <v>433</v>
+      </c>
       <c r="C22" s="8"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="B23" s="8"/>
+      <c r="B23" s="8" t="s">
+        <v>433</v>
+      </c>
       <c r="C23" s="8"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="B24" s="8"/>
+      <c r="B24" s="8" t="s">
+        <v>433</v>
+      </c>
       <c r="C24" s="8"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="B25" s="8"/>
+      <c r="B25" s="8" t="s">
+        <v>433</v>
+      </c>
       <c r="C25" s="8"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="B26" s="8"/>
+      <c r="B26" s="8" t="s">
+        <v>433</v>
+      </c>
       <c r="C26" s="8"/>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="B27" s="8"/>
+      <c r="B27" s="8" t="s">
+        <v>433</v>
+      </c>
       <c r="C27" s="8"/>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="B28" s="8"/>
+      <c r="B28" s="8" t="s">
+        <v>433</v>
+      </c>
       <c r="C28" s="8"/>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="B29" s="8"/>
+      <c r="B29" s="8" t="s">
+        <v>433</v>
+      </c>
       <c r="C29" s="8"/>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="B30" s="8"/>
+      <c r="B30" s="8" t="s">
+        <v>433</v>
+      </c>
       <c r="C30" s="8"/>
     </row>
   </sheetData>
@@ -4527,12 +4806,12 @@
   <sheetData>
     <row r="1" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>145</v>
+        <v>534</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -4543,205 +4822,359 @@
         <v>88</v>
       </c>
       <c r="C4" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D4" s="10" t="s">
         <v>147</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>148</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>130</v>
       </c>
       <c r="F4" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="G4" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="H4" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="I4" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="J4" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="J4" s="10" t="s">
+      <c r="K4" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="K4" s="10" t="s">
+      <c r="L4" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="L4" s="10" t="s">
+      <c r="M4" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="M4" s="10" t="s">
+      <c r="N4" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="N4" s="10" t="s">
+      <c r="O4" s="10" t="s">
         <v>157</v>
-      </c>
-      <c r="O4" s="10" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>94</v>
       </c>
       <c r="C5" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="D5" s="14" t="s">
         <v>160</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>161</v>
       </c>
       <c r="E5" s="14" t="s">
         <v>133</v>
       </c>
       <c r="F5" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="G5" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="G5" s="14" t="s">
+      <c r="H5" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="H5" s="14" t="s">
+      <c r="I5" s="14" t="s">
         <v>164</v>
       </c>
-      <c r="I5" s="14" t="s">
+      <c r="J5" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="J5" s="14" t="s">
+      <c r="K5" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="K5" s="14" t="s">
+      <c r="L5" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="L5" s="14" t="s">
+      <c r="M5" s="14" t="s">
         <v>168</v>
-      </c>
-      <c r="M5" s="14" t="s">
-        <v>169</v>
       </c>
       <c r="N5" s="14"/>
       <c r="O5" s="14"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>541</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>453</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>537</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>539</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>535</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>552</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>536</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>538</v>
+      </c>
+      <c r="M6" s="8" t="s">
+        <v>444</v>
+      </c>
+      <c r="N6" s="8"/>
+      <c r="O6" s="8" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
-      <c r="M6" s="8"/>
-      <c r="N6" s="8"/>
-      <c r="O6" s="8"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
+      <c r="B7" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>542</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>525</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>543</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>544</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>545</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>536</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>546</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>444</v>
+      </c>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
-      <c r="N7" s="8"/>
-      <c r="O7" s="8"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
+      <c r="B8" s="8" t="s">
+        <v>467</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>442</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>548</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>549</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>555</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>556</v>
+      </c>
+      <c r="M8" s="8" t="s">
+        <v>462</v>
+      </c>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
-      <c r="N8" s="8"/>
-      <c r="O8" s="8"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
+      <c r="B9" s="8" t="s">
+        <v>487</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>557</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>461</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>507</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>558</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>559</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>560</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>561</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>562</v>
+      </c>
+      <c r="M9" s="8" t="s">
+        <v>444</v>
+      </c>
+      <c r="N9" s="8"/>
+      <c r="O9" s="8" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8"/>
-      <c r="N9" s="8"/>
-      <c r="O9" s="8"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
+      <c r="B10" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>564</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>453</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>500</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>565</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>566</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>567</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>568</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>569</v>
+      </c>
+      <c r="M10" s="8" t="s">
+        <v>444</v>
+      </c>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8"/>
-      <c r="N10" s="8"/>
-      <c r="O10" s="8"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
+      <c r="B11" s="8" t="s">
+        <v>488</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>595</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>505</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>571</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>572</v>
+      </c>
       <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="8"/>
+      <c r="K11" s="8" t="s">
+        <v>573</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>574</v>
+      </c>
+      <c r="M11" s="8" t="s">
+        <v>444</v>
+      </c>
       <c r="N11" s="8"/>
-      <c r="O11" s="8"/>
+      <c r="O11" s="8" t="s">
+        <v>575</v>
+      </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
@@ -4760,7 +5193,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -4779,7 +5212,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -4798,7 +5231,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
@@ -4817,7 +5250,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
@@ -4836,7 +5269,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
@@ -4855,7 +5288,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
@@ -4874,7 +5307,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
@@ -4893,7 +5326,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
@@ -4912,7 +5345,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
@@ -4931,7 +5364,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
@@ -4950,7 +5383,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
@@ -4969,7 +5402,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
@@ -4988,7 +5421,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
@@ -5007,7 +5440,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
@@ -5026,7 +5459,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
@@ -5045,7 +5478,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
@@ -5064,7 +5497,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
@@ -5083,7 +5516,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
@@ -5102,7 +5535,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
@@ -5121,7 +5554,7 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
@@ -5140,7 +5573,7 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
@@ -5159,7 +5592,7 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
@@ -5178,7 +5611,7 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B35" s="8"/>
       <c r="C35" s="8"/>
@@ -5197,7 +5630,7 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" s="7" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B36" s="8"/>
       <c r="C36" s="8"/>
@@ -5216,7 +5649,7 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" s="7" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
@@ -5235,7 +5668,7 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" s="7" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B38" s="8"/>
       <c r="C38" s="8"/>
@@ -5254,7 +5687,7 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" s="7" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B39" s="8"/>
       <c r="C39" s="8"/>
@@ -5273,7 +5706,7 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B40" s="8"/>
       <c r="C40" s="8"/>
@@ -5292,7 +5725,7 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B41" s="8"/>
       <c r="C41" s="8"/>
@@ -5311,7 +5744,7 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B42" s="8"/>
       <c r="C42" s="8"/>
@@ -5330,7 +5763,7 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B43" s="8"/>
       <c r="C43" s="8"/>
@@ -5349,7 +5782,7 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" s="7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B44" s="8"/>
       <c r="C44" s="8"/>
@@ -5368,7 +5801,7 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45" s="7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B45" s="8"/>
       <c r="C45" s="8"/>
@@ -5464,12 +5897,12 @@
   <sheetData>
     <row r="1" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -5477,16 +5910,16 @@
         <v>64</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C4" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="E4" s="10" t="s">
         <v>212</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>213</v>
       </c>
       <c r="F4" s="10" t="s">
         <v>130</v>
@@ -5495,45 +5928,45 @@
         <v>38</v>
       </c>
       <c r="H4" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="I4" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="J4" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="J4" s="10" t="s">
+      <c r="K4" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="L4" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="M4" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="N4" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="K4" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="L4" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="M4" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="N4" s="10" t="s">
+      <c r="O4" s="10" t="s">
         <v>217</v>
-      </c>
-      <c r="O4" s="10" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="B5" s="14" t="s">
         <v>219</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="C5" s="14" t="s">
         <v>220</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="D5" s="14" t="s">
         <v>221</v>
       </c>
-      <c r="D5" s="14" t="s">
-        <v>222</v>
-      </c>
       <c r="E5" s="14" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F5" s="14" t="s">
         <v>133</v>
@@ -5545,144 +5978,300 @@
         <v>43</v>
       </c>
       <c r="I5" s="14" t="s">
+        <v>222</v>
+      </c>
+      <c r="J5" s="14" t="s">
         <v>223</v>
       </c>
-      <c r="J5" s="14" t="s">
+      <c r="K5" s="14" t="s">
         <v>224</v>
       </c>
-      <c r="K5" s="14" t="s">
+      <c r="L5" s="14" t="s">
         <v>225</v>
       </c>
-      <c r="L5" s="14" t="s">
+      <c r="M5" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="M5" s="14" t="s">
+      <c r="N5" s="14" t="s">
         <v>227</v>
       </c>
-      <c r="N5" s="14" t="s">
+      <c r="O5" s="14" t="s">
         <v>228</v>
       </c>
-      <c r="O5" s="14" t="s">
+    </row>
+    <row r="6" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
+      <c r="B6" s="8" t="s">
+        <v>576</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>541</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>577</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>583</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>592</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>584</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>585</v>
+      </c>
+      <c r="M6" s="8"/>
+      <c r="N6" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="O6" s="8" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
-      <c r="M6" s="8"/>
-      <c r="N6" s="8"/>
-      <c r="O6" s="8"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
+      <c r="B7" s="8" t="s">
+        <v>525</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>452</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>542</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>578</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>586</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>591</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>587</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>588</v>
+      </c>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="O7" s="8" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
-      <c r="N7" s="8"/>
-      <c r="O7" s="8"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
+      <c r="B8" s="8" t="s">
+        <v>589</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>564</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>579</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>566</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>590</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>593</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>594</v>
+      </c>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="O8" s="8" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
-      <c r="N8" s="8"/>
-      <c r="O8" s="8"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
+      <c r="B9" s="8" t="s">
+        <v>505</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>488</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>596</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>580</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>572</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>597</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>598</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>600</v>
+      </c>
+      <c r="M9" s="8"/>
+      <c r="N9" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="O9" s="8" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8"/>
-      <c r="N9" s="8"/>
-      <c r="O9" s="8"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
+      <c r="B10" s="8" t="s">
+        <v>507</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>557</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>581</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>566</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>599</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>601</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>602</v>
+      </c>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="O10" s="8" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8"/>
-      <c r="N10" s="8"/>
-      <c r="O10" s="8"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
-        <v>235</v>
-      </c>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
+      <c r="B11" s="8" t="s">
+        <v>548</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>467</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>582</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>549</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>603</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>604</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>605</v>
+      </c>
       <c r="M11" s="8"/>
-      <c r="N11" s="8"/>
-      <c r="O11" s="8"/>
+      <c r="N11" s="8" t="s">
+        <v>463</v>
+      </c>
+      <c r="O11" s="8" t="s">
+        <v>473</v>
+      </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
@@ -5701,7 +6290,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -5720,7 +6309,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -5739,7 +6328,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
@@ -5758,7 +6347,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
@@ -5777,7 +6366,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
@@ -5796,7 +6385,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
@@ -5815,7 +6404,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
@@ -5834,7 +6423,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
@@ -5853,7 +6442,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
@@ -5872,7 +6461,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
@@ -5891,7 +6480,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
@@ -5910,7 +6499,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
@@ -5929,7 +6518,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
@@ -5948,7 +6537,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
@@ -5967,7 +6556,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
@@ -5986,7 +6575,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
@@ -6005,7 +6594,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
@@ -6024,7 +6613,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
@@ -6043,7 +6632,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
@@ -6062,7 +6651,7 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
@@ -6081,7 +6670,7 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
@@ -6100,7 +6689,7 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
@@ -6119,7 +6708,7 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B35" s="8"/>
       <c r="C35" s="8"/>
@@ -6221,12 +6810,12 @@
   <sheetData>
     <row r="1" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6240,60 +6829,60 @@
         <v>88</v>
       </c>
       <c r="D4" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="E4" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="F4" s="10" t="s">
         <v>263</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="G4" s="10" t="s">
         <v>264</v>
       </c>
-      <c r="G4" s="10" t="s">
-        <v>265</v>
-      </c>
       <c r="H4" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="I4" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="J4" s="10" t="s">
         <v>157</v>
-      </c>
-      <c r="J4" s="10" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>138</v>
       </c>
       <c r="C5" s="14" t="s">
+        <v>266</v>
+      </c>
+      <c r="D5" s="14" t="s">
         <v>267</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="E5" s="14" t="s">
         <v>268</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="F5" s="14" t="s">
         <v>269</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="G5" s="14" t="s">
         <v>270</v>
       </c>
-      <c r="G5" s="14" t="s">
-        <v>271</v>
-      </c>
       <c r="H5" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I5" s="14"/>
       <c r="J5" s="14" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>137</v>
@@ -6309,7 +6898,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>138</v>
@@ -6325,7 +6914,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>139</v>
@@ -6341,7 +6930,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>140</v>
@@ -6357,7 +6946,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>141</v>
@@ -6373,7 +6962,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>142</v>
@@ -6389,7 +6978,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>143</v>
@@ -6405,7 +6994,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -6419,7 +7008,7 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -6433,7 +7022,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
@@ -6447,7 +7036,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
@@ -6461,7 +7050,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
@@ -6475,7 +7064,7 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
@@ -6489,7 +7078,7 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
@@ -6503,7 +7092,7 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
@@ -6573,12 +7162,12 @@
   <sheetData>
     <row r="1" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6586,57 +7175,57 @@
         <v>64</v>
       </c>
       <c r="B4" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="C4" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="D4" s="10" t="s">
         <v>291</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="E4" s="10" t="s">
         <v>292</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="F4" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="F4" s="10" t="s">
-        <v>294</v>
-      </c>
       <c r="G4" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="H4" s="10" t="s">
         <v>155</v>
-      </c>
-      <c r="H4" s="10" t="s">
-        <v>156</v>
       </c>
       <c r="I4" s="10" t="s">
         <v>88</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
+        <v>294</v>
+      </c>
+      <c r="B5" s="14" t="s">
         <v>295</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="C5" s="14" t="s">
         <v>296</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="D5" s="14" t="s">
         <v>297</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="E5" s="14" t="s">
         <v>298</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="F5" s="14" t="s">
         <v>299</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="G5" s="14" t="s">
         <v>300</v>
       </c>
-      <c r="G5" s="14" t="s">
-        <v>301</v>
-      </c>
       <c r="H5" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I5" s="14" t="s">
         <v>94</v>
@@ -6645,7 +7234,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -6659,7 +7248,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
@@ -6673,7 +7262,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
@@ -6687,7 +7276,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
@@ -6701,7 +7290,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
@@ -6715,7 +7304,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
@@ -6729,7 +7318,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
@@ -6743,7 +7332,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -6757,7 +7346,7 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -6771,7 +7360,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
@@ -6785,7 +7374,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
@@ -6799,7 +7388,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
@@ -6813,7 +7402,7 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
@@ -6827,7 +7416,7 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
@@ -6841,7 +7430,7 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
@@ -6855,7 +7444,7 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
@@ -6869,7 +7458,7 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
@@ -6883,7 +7472,7 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
@@ -6897,7 +7486,7 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
@@ -6911,7 +7500,7 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
